--- a/Docs/Auswertung.xlsx
+++ b/Docs/Auswertung.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekte\GitHub\Vergleichsprogramm\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32425DE9-C691-4971-9B2A-92768153BAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C59F58-2FA5-4C33-8AF1-7F61ED2A9558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{388948E0-F48B-4D39-A8BF-521842870DDC}"/>
   </bookViews>
@@ -319,9 +319,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -359,7 +359,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -465,7 +465,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -607,7 +607,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -749,11 +749,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4479C0AE-B510-4E7D-B6C5-BA39171D2D0A}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="44.73046875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.33203125" customWidth="1"/>
+    <col min="6" max="7" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="2.59765625" customWidth="1"/>
   </cols>
@@ -1251,6 +1253,32 @@
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
     </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="C16" s="2">
+        <f>(C2+C3+C10+C11+C12)*1000</f>
+        <v>110.496</v>
+      </c>
+      <c r="D16" s="2">
+        <f>(D2+D3+D10+D11+D12)*1000</f>
+        <v>525.15200000000004</v>
+      </c>
+      <c r="E16" s="2">
+        <f>(E2+E3+E10+E11+E12)*1000</f>
+        <v>1468.9999999999995</v>
+      </c>
+      <c r="F16" s="2">
+        <f>(F2+F3+F10+F11+F12)*1000</f>
+        <v>1196</v>
+      </c>
+      <c r="G16" s="2">
+        <f>(G2+G3+G10+G11+G12)*1000</f>
+        <v>2774.3519999999994</v>
+      </c>
+      <c r="I16" s="2">
+        <f>(I2+I3+I10+I11+I12)*1000</f>
+        <v>75.543999999999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
